--- a/src/test/resources/dataFiles/excelFiles/correctAutomationWithStatus.xlsx
+++ b/src/test/resources/dataFiles/excelFiles/correctAutomationWithStatus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\blocrecon\src\test\resources\dataFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\blocrecon\src\test\resources\dataFiles\excelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC862B0E-6C9C-4086-9489-29895920E4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E5E61C-DADF-4CEB-80D0-8B0F84ABB0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{CA011A21-70A2-4DF5-AE26-B4AB6324FE8A}"/>
   </bookViews>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1056284F-62D9-473F-BECF-60E2542248EF}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -488,10 +488,11 @@
     <col min="9" max="11" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,8 +535,9 @@
       <c r="N1" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -576,7 +578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -617,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -658,7 +660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -699,7 +701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -740,7 +742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -781,7 +783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -822,7 +824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -863,7 +865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -904,7 +906,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -945,7 +947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -986,7 +988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1027,7 +1029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
